--- a/output/pdf_financials_xlsx/MBI.H.xlsx
+++ b/output/pdf_financials_xlsx/MBI.H.xlsx
@@ -1907,40 +1907,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.181507</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.144306</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.022991</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.045463</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.000629</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.002398</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.010965</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.009193</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.000407</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000713</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.00088</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="35">
@@ -1993,40 +1993,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.181507</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.144306</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.022991</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.045463</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.000629</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.002398</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.010965</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.009193</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.000407</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.000713</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.00088</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="37">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/MBI.H.xlsx
+++ b/output/pdf_financials_xlsx/MBI.H.xlsx
@@ -11626,7 +11626,11 @@
           <t>Shares issued for cash 2,000,000</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -13742,7 +13746,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
